--- a/admin/data/todayTeaPool.xlsx
+++ b/admin/data/todayTeaPool.xlsx
@@ -1394,7 +1394,7 @@
     <t>과일양갱</t>
   </si>
   <si>
-    <t>촉촉 속에서 작은 온기를 느끼고 싶은 날</t>
+    <t>촉촉함 속에서 작은 온기를 느끼고 싶은</t>
   </si>
   <si>
     <t>오늘은 조금 천천히 가도 좋으니까 현미녹차 한 잔 해보세요. 구수한 현미 향과 편안한 녹차 맛이 축축한 공기 속에서 작은 온기를 느끼고 싶은 마음과 잘 어울리니 80℃ 안팎 · 2분으로 우려 유과과 함께 즐겨보세요.</t>
